--- a/server/CRM/CRM/wwwroot/Templates/ThongTinKhachHang.xlsx
+++ b/server/CRM/CRM/wwwroot/Templates/ThongTinKhachHang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRM\CRM\server\CRM\CRM\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB57148D-451B-428C-A37C-59059FA384BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157F88D0-873B-4A03-A67B-2A3759F5A8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -136,7 +136,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87B1377-5947-465F-93BB-487646B99284}">
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18.88671875" style="2" customWidth="1"/>
@@ -533,300 +533,6 @@
       <c r="K2" s="4"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" s="4"/>
-    </row>
-    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="4"/>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="4"/>
-    </row>
-    <row r="38" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K38" s="4"/>
-    </row>
-    <row r="39" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K57" s="4"/>
-    </row>
-    <row r="58" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K58" s="4"/>
-    </row>
-    <row r="59" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K59" s="4"/>
-    </row>
-    <row r="60" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K60" s="4"/>
-    </row>
-    <row r="61" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K61" s="4"/>
-    </row>
-    <row r="62" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K62" s="4"/>
-    </row>
-    <row r="63" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K63" s="4"/>
-    </row>
-    <row r="64" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K64" s="4"/>
-    </row>
-    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K65" s="4"/>
-    </row>
-    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K66" s="4"/>
-    </row>
-    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K67" s="4"/>
-    </row>
-    <row r="68" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K69" s="4"/>
-    </row>
-    <row r="70" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K70" s="4"/>
-    </row>
-    <row r="71" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K71" s="4"/>
-    </row>
-    <row r="72" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K72" s="4"/>
-    </row>
-    <row r="73" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K73" s="4"/>
-    </row>
-    <row r="74" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K74" s="4"/>
-    </row>
-    <row r="75" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K75" s="4"/>
-    </row>
-    <row r="76" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K76" s="4"/>
-    </row>
-    <row r="77" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K77" s="4"/>
-    </row>
-    <row r="78" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K78" s="4"/>
-    </row>
-    <row r="79" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K79" s="4"/>
-    </row>
-    <row r="80" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K80" s="4"/>
-    </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K81" s="4"/>
-    </row>
-    <row r="82" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K82" s="4"/>
-    </row>
-    <row r="83" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K83" s="4"/>
-    </row>
-    <row r="84" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K84" s="4"/>
-    </row>
-    <row r="85" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K85" s="4"/>
-    </row>
-    <row r="86" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K86" s="4"/>
-    </row>
-    <row r="87" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K87" s="4"/>
-    </row>
-    <row r="88" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K88" s="4"/>
-    </row>
-    <row r="89" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K89" s="4"/>
-    </row>
-    <row r="90" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K90" s="4"/>
-    </row>
-    <row r="91" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K91" s="4"/>
-    </row>
-    <row r="92" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K92" s="4"/>
-    </row>
-    <row r="93" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K93" s="4"/>
-    </row>
-    <row r="94" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K94" s="4"/>
-    </row>
-    <row r="95" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K95" s="4"/>
-    </row>
-    <row r="96" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K96" s="4"/>
-    </row>
-    <row r="97" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K97" s="4"/>
-    </row>
-    <row r="98" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K98" s="4"/>
-    </row>
-    <row r="99" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K99" s="4"/>
-    </row>
-    <row r="100" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K100" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F100" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
@@ -841,16 +547,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I100" xr:uid="{E4EE7E7B-BE2F-475B-8863-A35DBA405826}">
       <formula1>"Kinh doanh thực phẩm , kinh doanh hóa mĩ phẩm ,Kinh doanh điện tử điện lạnh, kinh doanh đồ gỗ, Kinh doanh hàng gia dụng , kinh doanh nông sản,Kinh doanh sắt thép , kinh doanh thương mại khác"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{0869C82E-FE33-4E08-BB8A-9FEBB18F4208}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L100" xr:uid="{0869C82E-FE33-4E08-BB8A-9FEBB18F4208}">
       <formula1>"Dưới 1 tỉ đồng , 1 tỉ đồng đến 3 tỉ đồng ,Từ 3 đến 5 tỉ đồng ,Trên 5 tỉ đồng"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P100" xr:uid="{AB5594FA-297D-4A82-8BD1-672AF30D7E71}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2" xr:uid="{AB5594FA-297D-4A82-8BD1-672AF30D7E71}">
       <formula1>"0 , 1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2" xr:uid="{0953E154-6A45-4CAD-9873-0AD892E1F145}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q100" xr:uid="{0953E154-6A45-4CAD-9873-0AD892E1F145}">
       <formula1>"0 ,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R101" xr:uid="{4BC7B3C6-05D8-4782-A120-1652E5E2BEBC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R100" xr:uid="{4BC7B3C6-05D8-4782-A120-1652E5E2BEBC}">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
